--- a/data/trans_orig/P04B3_1_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P04B3_1_2023-Clase-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si percibe la temperatura en la vivienda durante el verano como un problema en 2023</t>
+          <t>Población según si percibe la temperatura en la vivienda durante el verano como un problema en 2023 (tasa de respuesta: 99,91%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>92190</t>
+          <t>93654</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>128664</t>
+          <t>129860</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>25,52%</t>
+          <t>25,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>67508</t>
+          <t>66803</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>95589</t>
+          <t>95602</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,7 +780,7 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,11%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>168056</t>
+          <t>169332</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>214160</t>
+          <t>215997</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,67%</t>
+          <t>17,81%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,52%</t>
+          <t>22,71%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>61747</t>
+          <t>62355</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>95478</t>
+          <t>96518</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,25%</t>
+          <t>12,37%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>19,14%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>43852</t>
+          <t>44014</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>66791</t>
+          <t>67731</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,82%</t>
+          <t>9,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>15,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>114020</t>
+          <t>111926</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>155282</t>
+          <t>154883</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,29%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>70208</t>
+          <t>69344</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>105350</t>
+          <t>105027</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,92%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>20,83%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>63217</t>
+          <t>64286</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>91622</t>
+          <t>90956</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>14,39%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>20,51%</t>
+          <t>20,36%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>143609</t>
+          <t>140734</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>188165</t>
+          <t>185322</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>15,1%</t>
+          <t>14,8%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>19,49%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>207585</t>
+          <t>207869</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>255351</t>
+          <t>252090</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>41,17%</t>
+          <t>41,23%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>50,65%</t>
+          <t>50,0%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>215404</t>
+          <t>215709</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>253180</t>
+          <t>252471</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>48,22%</t>
+          <t>48,29%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>56,67%</t>
+          <t>56,51%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>434685</t>
+          <t>434310</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>495835</t>
+          <t>494692</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>45,71%</t>
+          <t>45,67%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>52,14%</t>
+          <t>52,02%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>90314</t>
+          <t>91581</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>125099</t>
+          <t>124807</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>27,6%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>77718</t>
+          <t>78419</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>106090</t>
+          <t>105858</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>27,73%</t>
+          <t>27,67%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>176702</t>
+          <t>175886</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>222396</t>
+          <t>220900</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>21,07%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>26,64%</t>
+          <t>26,46%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>44225</t>
+          <t>44829</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>75717</t>
+          <t>73841</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,33%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>44683</t>
+          <t>44493</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>69638</t>
+          <t>69666</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>11,63%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>18,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>98256</t>
+          <t>96845</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>134827</t>
+          <t>134785</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,7 +1497,7 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>63492</t>
+          <t>61644</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>99021</t>
+          <t>97511</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,04%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>52510</t>
+          <t>53087</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>78579</t>
+          <t>78104</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13,73%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>122197</t>
+          <t>122901</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>165176</t>
+          <t>166621</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>14,64%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>19,96%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>184695</t>
+          <t>184825</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>228278</t>
+          <t>228896</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>40,84%</t>
+          <t>40,87%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>50,48%</t>
+          <t>50,62%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>152463</t>
+          <t>153423</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>186861</t>
+          <t>185995</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>39,85%</t>
+          <t>40,1%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>48,84%</t>
+          <t>48,62%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>349897</t>
+          <t>348941</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>404105</t>
+          <t>405594</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>41,91%</t>
+          <t>41,8%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>48,41%</t>
+          <t>48,59%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>38645</t>
+          <t>38787</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>174646</t>
+          <t>176587</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,78%</t>
+          <t>5,8%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>26,13%</t>
+          <t>26,42%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>35354</t>
+          <t>35380</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>53871</t>
+          <t>54497</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>21,26%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>32,4%</t>
+          <t>32,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>64050</t>
+          <t>66897</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>219006</t>
+          <t>220036</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>8,02%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>26,37%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>21951</t>
+          <t>26893</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>107442</t>
+          <t>109253</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,12 +1996,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>15515</t>
+          <t>15142</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>28304</t>
+          <t>28287</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,11%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>17,02%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>32912</t>
+          <t>39000</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>130168</t>
+          <t>127254</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,25%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>27794</t>
+          <t>27025</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>119431</t>
+          <t>122872</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>18,39%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>18491</t>
+          <t>18695</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>33144</t>
+          <t>32904</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,24%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>19,79%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>36074</t>
+          <t>36946</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>142600</t>
+          <t>142671</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,09%</t>
+          <t>17,1%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>278164</t>
+          <t>276391</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>574321</t>
+          <t>576739</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>41,62%</t>
+          <t>41,36%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>85,94%</t>
+          <t>86,3%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>64976</t>
+          <t>66439</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>85810</t>
+          <t>86697</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>39,08%</t>
+          <t>39,96%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>51,61%</t>
+          <t>52,15%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>356531</t>
+          <t>356435</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>699897</t>
+          <t>688899</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>42,72%</t>
+          <t>42,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>83,87%</t>
+          <t>82,55%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>223083</t>
+          <t>224181</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>283768</t>
+          <t>278245</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>26,89%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>68990</t>
+          <t>70245</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>179523</t>
+          <t>177915</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,05%</t>
+          <t>7,18%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>18,36%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>275613</t>
+          <t>259779</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>442087</t>
+          <t>443225</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>21,96%</t>
+          <t>22,02%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>94454</t>
+          <t>93837</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>135721</t>
+          <t>134484</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>13,12%</t>
+          <t>13,0%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>58924</t>
+          <t>62288</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>156197</t>
+          <t>154631</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>165307</t>
+          <t>157716</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>269535</t>
+          <t>269684</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,4%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>168206</t>
+          <t>167542</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>227049</t>
+          <t>228358</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>22,07%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>64732</t>
+          <t>62950</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>163325</t>
+          <t>163134</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>6,44%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>16,7%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>221069</t>
+          <t>210153</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>368633</t>
+          <t>369847</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,12 +2748,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,44%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>18,38%</t>
         </is>
       </c>
     </row>
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>441201</t>
+          <t>439650</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>510817</t>
+          <t>511163</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>42,64%</t>
+          <t>42,49%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>49,36%</t>
+          <t>49,4%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>493173</t>
+          <t>492030</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>779929</t>
+          <t>780810</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2826,12 +2826,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>50,43%</t>
+          <t>50,31%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>79,75%</t>
+          <t>79,84%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>956115</t>
+          <t>954871</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1346540</t>
+          <t>1390178</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>47,5%</t>
+          <t>47,44%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>66,9%</t>
+          <t>69,07%</t>
         </is>
       </c>
     </row>
@@ -3006,12 +3006,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>111710</t>
+          <t>114322</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>151450</t>
+          <t>153474</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3021,12 +3021,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>23,52%</t>
+          <t>24,07%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>31,88%</t>
+          <t>32,31%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3041,12 +3041,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>212420</t>
+          <t>212110</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>417697</t>
+          <t>412296</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3056,12 +3056,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>25,27%</t>
+          <t>25,23%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>49,68%</t>
+          <t>49,04%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3076,12 +3076,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>337769</t>
+          <t>342727</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>573418</t>
+          <t>565858</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3091,12 +3091,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>25,67%</t>
+          <t>26,05%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>43,58%</t>
+          <t>43,01%</t>
         </is>
       </c>
     </row>
@@ -3119,12 +3119,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>54660</t>
+          <t>54837</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>86673</t>
+          <t>84375</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3134,12 +3134,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,51%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>18,25%</t>
+          <t>17,76%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3154,12 +3154,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>88849</t>
+          <t>88439</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>142897</t>
+          <t>141378</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>17,0%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3189,12 +3189,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>153855</t>
+          <t>152182</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>213333</t>
+          <t>211871</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>11,57%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,1%</t>
         </is>
       </c>
     </row>
@@ -3232,12 +3232,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>57110</t>
+          <t>57318</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>90402</t>
+          <t>88299</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3247,12 +3247,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>12,02%</t>
+          <t>12,07%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>18,59%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3267,12 +3267,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>83878</t>
+          <t>88103</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>133757</t>
+          <t>136398</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>16,22%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3302,12 +3302,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>152575</t>
+          <t>153684</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>212362</t>
+          <t>212964</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,68%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>16,19%</t>
         </is>
       </c>
     </row>
@@ -3345,12 +3345,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>181682</t>
+          <t>177812</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>227174</t>
+          <t>224620</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3360,12 +3360,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>38,25%</t>
+          <t>37,43%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>47,82%</t>
+          <t>47,28%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>250101</t>
+          <t>255439</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>388294</t>
+          <t>395217</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3395,12 +3395,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>30,38%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>46,19%</t>
+          <t>47,01%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>452169</t>
+          <t>447565</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>598731</t>
+          <t>596877</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3430,12 +3430,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>34,37%</t>
+          <t>34,02%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>45,5%</t>
+          <t>45,36%</t>
         </is>
       </c>
     </row>
@@ -3575,12 +3575,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>38340</t>
+          <t>38568</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>78272</t>
+          <t>78196</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3590,12 +3590,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>15,95%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>32,57%</t>
+          <t>32,54%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3610,12 +3610,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>195554</t>
+          <t>200218</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>242787</t>
+          <t>246660</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3625,12 +3625,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>26,3%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>31,89%</t>
+          <t>32,4%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3645,12 +3645,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>249300</t>
+          <t>249206</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>311744</t>
+          <t>308821</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3660,12 +3660,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>24,89%</t>
+          <t>24,88%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>30,83%</t>
         </is>
       </c>
     </row>
@@ -3688,12 +3688,12 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>16272</t>
+          <t>17143</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>48916</t>
+          <t>50003</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3703,12 +3703,12 @@
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>6,77%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>20,35%</t>
+          <t>20,8%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3723,12 +3723,12 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>63426</t>
+          <t>64468</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>93221</t>
+          <t>93950</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -3738,12 +3738,12 @@
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3758,12 +3758,12 @@
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>85202</t>
+          <t>87321</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>129096</t>
+          <t>131635</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3773,12 +3773,12 @@
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>8,72%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>12,89%</t>
+          <t>13,14%</t>
         </is>
       </c>
     </row>
@@ -3801,12 +3801,12 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>19026</t>
+          <t>19190</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>59415</t>
+          <t>60832</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -3816,12 +3816,12 @@
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>24,72%</t>
+          <t>25,31%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>110542</t>
+          <t>111827</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>152310</t>
+          <t>152623</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3851,12 +3851,12 @@
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>14,52%</t>
+          <t>14,69%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="Q31" s="2" t="inlineStr">
@@ -3871,12 +3871,12 @@
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>141705</t>
+          <t>139829</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>201739</t>
+          <t>196680</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
@@ -3886,12 +3886,12 @@
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>13,96%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>19,63%</t>
         </is>
       </c>
     </row>
@@ -3914,12 +3914,12 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>92544</t>
+          <t>91882</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>144222</t>
+          <t>145396</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -3929,12 +3929,12 @@
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>38,5%</t>
+          <t>38,23%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>60,01%</t>
+          <t>60,5%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3949,12 +3949,12 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>304814</t>
+          <t>304313</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>360070</t>
+          <t>356489</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
@@ -3964,12 +3964,12 @@
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>40,03%</t>
+          <t>39,97%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>47,29%</t>
+          <t>46,82%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3984,12 +3984,12 @@
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>413277</t>
+          <t>415097</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>489219</t>
+          <t>493238</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
@@ -3999,12 +3999,12 @@
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>41,26%</t>
+          <t>41,44%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>48,84%</t>
+          <t>49,24%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>598714</t>
+          <t>567216</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>840827</t>
+          <t>841334</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>17,74%</t>
+          <t>16,81%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>24,93%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>712908</t>
+          <t>724795</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>1003805</t>
+          <t>1010394</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>19,94%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>28,26%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>1398990</t>
+          <t>1402833</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>1789290</t>
+          <t>1776712</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>25,56%</t>
         </is>
       </c>
     </row>
@@ -4257,12 +4257,12 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>321445</t>
+          <t>315066</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>464918</t>
+          <t>461063</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -4272,12 +4272,12 @@
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,66%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4292,12 +4292,12 @@
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>368698</t>
+          <t>363086</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>491504</t>
+          <t>490105</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>10,15%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4327,12 +4327,12 @@
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>730057</t>
+          <t>740352</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>928411</t>
+          <t>942577</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>10,5%</t>
+          <t>10,65%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>13,36%</t>
+          <t>13,56%</t>
         </is>
       </c>
     </row>
@@ -4370,12 +4370,12 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>428492</t>
+          <t>410946</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>605219</t>
+          <t>602480</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -4385,12 +4385,12 @@
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>12,7%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4405,12 +4405,12 @@
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>441136</t>
+          <t>443747</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>589861</t>
+          <t>589428</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,41%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>16,5%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4440,12 +4440,12 @@
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>915636</t>
+          <t>933644</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>1166661</t>
+          <t>1165584</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>16,77%</t>
         </is>
       </c>
     </row>
@@ -4483,12 +4483,12 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1503148</t>
+          <t>1513176</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2056437</t>
+          <t>2135626</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>44,54%</t>
+          <t>44,84%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>60,93%</t>
+          <t>63,28%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4518,12 +4518,12 @@
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>1605781</t>
+          <t>1600683</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>2058759</t>
+          <t>2096566</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
@@ -4533,12 +4533,12 @@
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>44,91%</t>
+          <t>44,77%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>57,58%</t>
+          <t>58,64%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4553,12 +4553,12 @@
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>3166517</t>
+          <t>3165090</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>3921044</t>
+          <t>3894822</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
@@ -4568,12 +4568,12 @@
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>45,56%</t>
+          <t>45,54%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>56,41%</t>
+          <t>56,04%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P04B3_1_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/P04B3_1_2023-Clase-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>110415</t>
+          <t>123434</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>93654</t>
+          <t>106224</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>129860</t>
+          <t>144129</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>21,9%</t>
+          <t>22,46%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>18,57%</t>
+          <t>19,33%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>25,76%</t>
+          <t>26,22%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>80873</t>
+          <t>92088</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>66803</t>
+          <t>76869</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>95602</t>
+          <t>108412</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>18,1%</t>
+          <t>18,88%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>15,76%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>22,23%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
+          <t>215523</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
           <t>191288</t>
         </is>
       </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>169332</t>
-        </is>
-      </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>215997</t>
+          <t>241245</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>20,12%</t>
+          <t>20,78%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>22,71%</t>
+          <t>23,26%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>78362</t>
+          <t>85102</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>62355</t>
+          <t>68045</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>96518</t>
+          <t>104857</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>15,54%</t>
+          <t>15,48%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>12,37%</t>
+          <t>12,38%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>19,14%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>54066</t>
+          <t>61373</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>44014</t>
+          <t>50358</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>67731</t>
+          <t>74187</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>12,1%</t>
+          <t>12,59%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>9,85%</t>
+          <t>10,33%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>15,16%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>132428</t>
+          <t>146476</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>111926</t>
+          <t>123667</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>154883</t>
+          <t>169341</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>13,93%</t>
+          <t>14,12%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>11,77%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>16,33%</t>
         </is>
       </c>
     </row>
@@ -951,17 +951,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>86414</t>
+          <t>94183</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>69344</t>
+          <t>76267</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>105027</t>
+          <t>115917</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>77110</t>
+          <t>86002</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>64286</t>
+          <t>70771</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>90956</t>
+          <t>100939</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>17,64%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,51%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>20,7%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>163524</t>
+          <t>180186</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>140734</t>
+          <t>158726</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>185322</t>
+          <t>208186</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>17,2%</t>
+          <t>17,37%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>14,8%</t>
+          <t>15,3%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>20,07%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>229006</t>
+          <t>246919</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>207869</t>
+          <t>221608</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>252090</t>
+          <t>271670</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>45,42%</t>
+          <t>44,92%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>41,23%</t>
+          <t>40,32%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>50,0%</t>
+          <t>49,43%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>234688</t>
+          <t>248200</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>215709</t>
+          <t>227884</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>252471</t>
+          <t>266001</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>52,53%</t>
+          <t>50,9%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>48,29%</t>
+          <t>46,73%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>56,51%</t>
+          <t>54,55%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>463693</t>
+          <t>495120</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>434310</t>
+          <t>463406</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>494692</t>
+          <t>526723</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>48,76%</t>
+          <t>47,73%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>45,67%</t>
+          <t>44,67%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>52,02%</t>
+          <t>50,78%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>504196</t>
+          <t>549639</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>504196</t>
+          <t>549639</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>504196</t>
+          <t>549639</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>446737</t>
+          <t>487664</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>446737</t>
+          <t>487664</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>446737</t>
+          <t>487664</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>950933</t>
+          <t>1037304</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>950933</t>
+          <t>1037304</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>950933</t>
+          <t>1037304</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>107578</t>
+          <t>119550</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>91581</t>
+          <t>100956</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>124807</t>
+          <t>137097</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>23,79%</t>
+          <t>24,74%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>20,89%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>27,6%</t>
+          <t>28,37%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>90797</t>
+          <t>101558</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>78419</t>
+          <t>87186</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>105858</t>
+          <t>117371</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>23,73%</t>
+          <t>24,0%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>20,5%</t>
+          <t>20,6%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>27,67%</t>
+          <t>27,74%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>198375</t>
+          <t>221108</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>175886</t>
+          <t>196279</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>220900</t>
+          <t>246226</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>23,76%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>21,07%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>26,46%</t>
+          <t>27,17%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>58637</t>
+          <t>63077</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>44829</t>
+          <t>49309</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>73841</t>
+          <t>80017</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>13,05%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>9,91%</t>
+          <t>10,2%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>16,33%</t>
+          <t>16,56%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>56565</t>
+          <t>63821</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>44493</t>
+          <t>51409</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>69666</t>
+          <t>77000</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>15,08%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>11,63%</t>
+          <t>12,15%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>18,21%</t>
+          <t>18,2%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>115201</t>
+          <t>126898</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>96845</t>
+          <t>107525</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>134785</t>
+          <t>149488</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,86%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>16,49%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>79069</t>
+          <t>85301</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>61644</t>
+          <t>66256</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>97511</t>
+          <t>105434</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,82%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>64248</t>
+          <t>74302</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>53087</t>
+          <t>59807</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>78104</t>
+          <t>90037</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>16,79%</t>
+          <t>17,56%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>14,13%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>21,28%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>143316</t>
+          <t>159603</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>122901</t>
+          <t>137770</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>166621</t>
+          <t>186177</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>17,61%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>15,2%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>19,96%</t>
+          <t>20,54%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>206930</t>
+          <t>215283</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>184825</t>
+          <t>191980</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>228896</t>
+          <t>236015</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>45,76%</t>
+          <t>44,55%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>40,87%</t>
+          <t>39,73%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>50,62%</t>
+          <t>48,84%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>170971</t>
+          <t>183462</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>153423</t>
+          <t>166596</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>185995</t>
+          <t>200356</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>44,69%</t>
+          <t>43,36%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>40,1%</t>
+          <t>39,37%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>48,62%</t>
+          <t>47,35%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>377901</t>
+          <t>398745</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>348941</t>
+          <t>370563</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>405594</t>
+          <t>429886</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>45,27%</t>
+          <t>43,99%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>41,8%</t>
+          <t>40,88%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>48,59%</t>
+          <t>47,43%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>452213</t>
+          <t>483212</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>382580</t>
+          <t>423143</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>834793</t>
+          <t>906355</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>105984</t>
+          <t>118412</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>38787</t>
+          <t>100976</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>176587</t>
+          <t>138350</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>15,86%</t>
+          <t>25,11%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>26,42%</t>
+          <t>29,34%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>44078</t>
+          <t>49244</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>35380</t>
+          <t>39739</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>54497</t>
+          <t>60184</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>26,51%</t>
+          <t>26,36%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>21,28%</t>
+          <t>21,27%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>32,78%</t>
+          <t>32,22%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>150062</t>
+          <t>167656</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>66897</t>
+          <t>146557</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>220036</t>
+          <t>191672</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>25,46%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>22,26%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>29,11%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>64977</t>
+          <t>70606</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>26893</t>
+          <t>55841</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>109253</t>
+          <t>85342</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>14,97%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>11,84%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>16,35%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,32 +2011,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>21091</t>
+          <t>25166</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>15142</t>
+          <t>18419</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>28287</t>
+          <t>32263</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>12,69%</t>
+          <t>13,47%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>9,11%</t>
+          <t>9,86%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>17,27%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>86068</t>
+          <t>95771</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>39000</t>
+          <t>80037</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>127254</t>
+          <t>114440</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>14,55%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>17,38%</t>
         </is>
       </c>
     </row>
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>71371</t>
+          <t>77736</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>27025</t>
+          <t>61664</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>122872</t>
+          <t>94523</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>16,48%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>13,08%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>18,39%</t>
+          <t>20,04%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>24899</t>
+          <t>28519</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>18695</t>
+          <t>20879</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>32904</t>
+          <t>37850</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>14,98%</t>
+          <t>15,27%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>11,24%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>20,26%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>96271</t>
+          <t>106256</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>36946</t>
+          <t>87255</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>142671</t>
+          <t>125385</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>19,04%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>425931</t>
+          <t>204858</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>276391</t>
+          <t>181729</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>576739</t>
+          <t>227249</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>63,74%</t>
+          <t>43,44%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>41,36%</t>
+          <t>38,53%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>86,3%</t>
+          <t>48,19%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>76187</t>
+          <t>83861</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>66439</t>
+          <t>72166</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>86697</t>
+          <t>96614</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>45,83%</t>
+          <t>44,9%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>39,96%</t>
+          <t>38,63%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>52,15%</t>
+          <t>51,72%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,32 +2272,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>502118</t>
+          <t>288720</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>356435</t>
+          <t>265024</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>688899</t>
+          <t>314645</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>60,17%</t>
+          <t>43,85%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>42,71%</t>
+          <t>40,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>82,55%</t>
+          <t>47,79%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>668264</t>
+          <t>471612</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>166255</t>
+          <t>186790</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>166255</t>
+          <t>186790</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>166255</t>
+          <t>186790</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>834519</t>
+          <t>658402</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>834519</t>
+          <t>658402</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>834519</t>
+          <t>658402</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>251023</t>
+          <t>287854</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>224181</t>
+          <t>259177</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>278245</t>
+          <t>318970</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>22,9%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>26,89%</t>
+          <t>28,18%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>135284</t>
+          <t>157406</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>70245</t>
+          <t>136621</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>177915</t>
+          <t>177308</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>13,83%</t>
+          <t>18,3%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>386308</t>
+          <t>445260</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>259779</t>
+          <t>405015</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>443225</t>
+          <t>485350</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>22,35%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>12,91%</t>
+          <t>20,33%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>22,02%</t>
+          <t>24,36%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>113570</t>
+          <t>129350</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>93837</t>
+          <t>105717</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>134484</t>
+          <t>152145</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>10,97%</t>
+          <t>11,43%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>9,07%</t>
+          <t>9,34%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>13,0%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>117217</t>
+          <t>134984</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>62288</t>
+          <t>117804</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>154631</t>
+          <t>155142</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>11,99%</t>
+          <t>15,69%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>13,69%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>230787</t>
+          <t>264334</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>157716</t>
+          <t>236024</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>269684</t>
+          <t>295770</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>11,47%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>11,85%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>14,85%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>194528</t>
+          <t>208614</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>167542</t>
+          <t>179625</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>228358</t>
+          <t>237600</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,43%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>20,99%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,32 +2693,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>123298</t>
+          <t>136193</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>62950</t>
+          <t>118620</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>163134</t>
+          <t>155588</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>6,44%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>16,68%</t>
+          <t>18,09%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>317826</t>
+          <t>344807</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>210153</t>
+          <t>314440</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>369847</t>
+          <t>387797</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>15,78%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>18,38%</t>
+          <t>19,47%</t>
         </is>
       </c>
     </row>
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>475698</t>
+          <t>506026</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>439650</t>
+          <t>472885</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>511163</t>
+          <t>542688</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>45,97%</t>
+          <t>44,71%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>42,49%</t>
+          <t>41,78%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>49,4%</t>
+          <t>47,95%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>602133</t>
+          <t>431660</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>492030</t>
+          <t>405690</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>780810</t>
+          <t>459040</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>61,57%</t>
+          <t>50,18%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>50,31%</t>
+          <t>47,16%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>79,84%</t>
+          <t>53,36%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1077831</t>
+          <t>937686</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>954871</t>
+          <t>889807</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1390178</t>
+          <t>977789</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>53,55%</t>
+          <t>47,07%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>47,44%</t>
+          <t>44,67%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>69,07%</t>
+          <t>49,08%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>1034819</t>
+          <t>1131843</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>977932</t>
+          <t>860243</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>977932</t>
+          <t>860243</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>977932</t>
+          <t>860243</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>2012751</t>
+          <t>1992086</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>2012751</t>
+          <t>1992086</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>2012751</t>
+          <t>1992086</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3001,32 +3001,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>130798</t>
+          <t>161439</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>114322</t>
+          <t>138481</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>153474</t>
+          <t>184958</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>27,53%</t>
+          <t>28,42%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>24,07%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>32,31%</t>
+          <t>32,57%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3036,32 +3036,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>274318</t>
+          <t>236020</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>212110</t>
+          <t>215162</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>412296</t>
+          <t>259750</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>32,63%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>25,23%</t>
+          <t>25,92%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>49,04%</t>
+          <t>31,29%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3071,32 +3071,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>405116</t>
+          <t>397459</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>342727</t>
+          <t>366545</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>565858</t>
+          <t>428042</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>26,05%</t>
+          <t>26,22%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>43,01%</t>
+          <t>30,62%</t>
         </is>
       </c>
     </row>
@@ -3114,32 +3114,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>68296</t>
+          <t>88043</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>54837</t>
+          <t>69514</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>84375</t>
+          <t>107263</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>14,38%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>17,76%</t>
+          <t>18,89%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3149,32 +3149,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>119477</t>
+          <t>140676</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>88439</t>
+          <t>123182</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>141378</t>
+          <t>159781</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>16,95%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>14,84%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>19,25%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3184,32 +3184,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>187773</t>
+          <t>228719</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>152182</t>
+          <t>203271</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>211871</t>
+          <t>256321</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>16,36%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,57%</t>
+          <t>14,54%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>18,33%</t>
         </is>
       </c>
     </row>
@@ -3227,32 +3227,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>72533</t>
+          <t>83617</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>57318</t>
+          <t>66128</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>88299</t>
+          <t>100704</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>15,27%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>12,07%</t>
+          <t>11,64%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>18,59%</t>
+          <t>17,73%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3262,32 +3262,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>114085</t>
+          <t>131970</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>88103</t>
+          <t>116573</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>136398</t>
+          <t>149420</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>16,22%</t>
+          <t>18,0%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3297,32 +3297,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>186618</t>
+          <t>215588</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>153684</t>
+          <t>192212</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>212964</t>
+          <t>240389</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>11,68%</t>
+          <t>13,75%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>17,19%</t>
         </is>
       </c>
     </row>
@@ -3340,32 +3340,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>203419</t>
+          <t>234865</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>177812</t>
+          <t>209673</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>224620</t>
+          <t>260045</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>42,82%</t>
+          <t>41,35%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>37,43%</t>
+          <t>36,92%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>47,28%</t>
+          <t>45,79%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3375,32 +3375,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>332836</t>
+          <t>321476</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>255439</t>
+          <t>297294</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>395217</t>
+          <t>344238</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>39,59%</t>
+          <t>38,73%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>30,38%</t>
+          <t>35,81%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>47,01%</t>
+          <t>41,47%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3410,32 +3410,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>536255</t>
+          <t>556340</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>447565</t>
+          <t>525018</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>596877</t>
+          <t>594941</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>40,76%</t>
+          <t>39,79%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>34,02%</t>
+          <t>37,55%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>45,36%</t>
+          <t>42,55%</t>
         </is>
       </c>
     </row>
@@ -3453,17 +3453,17 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>475046</t>
+          <t>567964</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>840715</t>
+          <t>830142</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>840715</t>
+          <t>830142</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>840715</t>
+          <t>830142</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3523,17 +3523,17 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1315761</t>
+          <t>1398106</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1315761</t>
+          <t>1398106</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1315761</t>
+          <t>1398106</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3555,7 +3555,7 @@
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B29" s="3" t="inlineStr">
@@ -3570,32 +3570,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>57303</t>
+          <t>70186</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>38568</t>
+          <t>52299</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>78196</t>
+          <t>92229</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>23,84%</t>
+          <t>29,79%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>22,2%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>32,54%</t>
+          <t>39,15%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3605,32 +3605,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>220611</t>
+          <t>255213</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>200218</t>
+          <t>229208</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>246660</t>
+          <t>281044</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>28,98%</t>
+          <t>30,23%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>26,3%</t>
+          <t>27,15%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>32,4%</t>
+          <t>33,29%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3640,32 +3640,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>277913</t>
+          <t>325399</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>249206</t>
+          <t>291727</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>308821</t>
+          <t>360834</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>27,74%</t>
+          <t>30,13%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>24,88%</t>
+          <t>27,02%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>30,83%</t>
+          <t>33,41%</t>
         </is>
       </c>
     </row>
@@ -3683,32 +3683,32 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>28903</t>
+          <t>25773</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>17143</t>
+          <t>14171</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>50003</t>
+          <t>44036</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>18,69%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3718,32 +3718,32 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>77611</t>
+          <t>90832</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>64468</t>
+          <t>73895</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>93950</t>
+          <t>109311</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,76%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>8,75%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>12,34%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3753,32 +3753,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>106513</t>
+          <t>116604</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>87321</t>
+          <t>96297</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>131635</t>
+          <t>142043</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>13,14%</t>
+          <t>13,15%</t>
         </is>
       </c>
     </row>
@@ -3796,32 +3796,32 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>35642</t>
+          <t>34399</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>19190</t>
+          <t>19104</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>60832</t>
+          <t>53649</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>14,83%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,11%</t>
         </is>
       </c>
       <c r="I31" s="2" t="inlineStr">
         <is>
-          <t>25,31%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="J31" s="2" t="inlineStr">
@@ -3831,27 +3831,27 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>131079</t>
+          <t>145906</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>111827</t>
+          <t>124613</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>152623</t>
+          <t>169273</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>17,28%</t>
         </is>
       </c>
       <c r="O31" s="2" t="inlineStr">
         <is>
-          <t>14,69%</t>
+          <t>14,76%</t>
         </is>
       </c>
       <c r="P31" s="2" t="inlineStr">
@@ -3866,32 +3866,32 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>166722</t>
+          <t>180306</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>139829</t>
+          <t>151637</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>196680</t>
+          <t>209312</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
         <is>
-          <t>16,64%</t>
+          <t>16,7%</t>
         </is>
       </c>
       <c r="V31" s="2" t="inlineStr">
         <is>
-          <t>13,96%</t>
+          <t>14,04%</t>
         </is>
       </c>
       <c r="W31" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>19,38%</t>
         </is>
       </c>
     </row>
@@ -3909,32 +3909,32 @@
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>118495</t>
+          <t>105227</t>
         </is>
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>91882</t>
+          <t>82584</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>145396</t>
+          <t>132726</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>49,3%</t>
+          <t>44,67%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>38,23%</t>
+          <t>35,05%</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
-          <t>60,5%</t>
+          <t>56,34%</t>
         </is>
       </c>
       <c r="J32" s="2" t="inlineStr">
@@ -3944,32 +3944,32 @@
       </c>
       <c r="K32" s="2" t="inlineStr">
         <is>
-          <t>332070</t>
+          <t>352330</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>304313</t>
+          <t>326302</t>
         </is>
       </c>
       <c r="M32" s="2" t="inlineStr">
         <is>
-          <t>356489</t>
+          <t>383369</t>
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr">
         <is>
-          <t>43,61%</t>
+          <t>41,73%</t>
         </is>
       </c>
       <c r="O32" s="2" t="inlineStr">
         <is>
-          <t>39,97%</t>
+          <t>38,65%</t>
         </is>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>46,82%</t>
+          <t>45,41%</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr">
@@ -3979,32 +3979,32 @@
       </c>
       <c r="R32" s="2" t="inlineStr">
         <is>
-          <t>450565</t>
+          <t>457557</t>
         </is>
       </c>
       <c r="S32" s="2" t="inlineStr">
         <is>
-          <t>415097</t>
+          <t>422218</t>
         </is>
       </c>
       <c r="T32" s="2" t="inlineStr">
         <is>
-          <t>493238</t>
+          <t>502430</t>
         </is>
       </c>
       <c r="U32" s="2" t="inlineStr">
         <is>
-          <t>44,98%</t>
+          <t>42,37%</t>
         </is>
       </c>
       <c r="V32" s="2" t="inlineStr">
         <is>
-          <t>41,44%</t>
+          <t>39,1%</t>
         </is>
       </c>
       <c r="W32" s="2" t="inlineStr">
         <is>
-          <t>49,24%</t>
+          <t>46,53%</t>
         </is>
       </c>
     </row>
@@ -4022,17 +4022,17 @@
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>240343</t>
+          <t>235585</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>240343</t>
+          <t>235585</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>240343</t>
+          <t>235585</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -4057,17 +4057,17 @@
       </c>
       <c r="K33" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="M33" s="2" t="inlineStr">
         <is>
-          <t>761371</t>
+          <t>844281</t>
         </is>
       </c>
       <c r="N33" s="2" t="inlineStr">
@@ -4092,17 +4092,17 @@
       </c>
       <c r="R33" s="2" t="inlineStr">
         <is>
-          <t>1001713</t>
+          <t>1079866</t>
         </is>
       </c>
       <c r="S33" s="2" t="inlineStr">
         <is>
-          <t>1001713</t>
+          <t>1079866</t>
         </is>
       </c>
       <c r="T33" s="2" t="inlineStr">
         <is>
-          <t>1001713</t>
+          <t>1079866</t>
         </is>
       </c>
       <c r="U33" s="2" t="inlineStr">
@@ -4139,32 +4139,32 @@
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>763100</t>
+          <t>880875</t>
         </is>
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>567216</t>
+          <t>826914</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>841334</t>
+          <t>931551</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>25,61%</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>16,81%</t>
+          <t>24,04%</t>
         </is>
       </c>
       <c r="I34" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="J34" s="2" t="inlineStr">
@@ -4174,32 +4174,32 @@
       </c>
       <c r="K34" s="2" t="inlineStr">
         <is>
-          <t>845961</t>
+          <t>891529</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>724795</t>
+          <t>842586</t>
         </is>
       </c>
       <c r="M34" s="2" t="inlineStr">
         <is>
-          <t>1010394</t>
+          <t>938267</t>
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>24,54%</t>
         </is>
       </c>
       <c r="O34" s="2" t="inlineStr">
         <is>
-          <t>20,27%</t>
+          <t>23,2%</t>
         </is>
       </c>
       <c r="P34" s="2" t="inlineStr">
         <is>
-          <t>28,26%</t>
+          <t>25,83%</t>
         </is>
       </c>
       <c r="Q34" s="2" t="inlineStr">
@@ -4209,32 +4209,32 @@
       </c>
       <c r="R34" s="2" t="inlineStr">
         <is>
-          <t>1609061</t>
+          <t>1772404</t>
         </is>
       </c>
       <c r="S34" s="2" t="inlineStr">
         <is>
-          <t>1402833</t>
+          <t>1698400</t>
         </is>
       </c>
       <c r="T34" s="2" t="inlineStr">
         <is>
-          <t>1776712</t>
+          <t>1841211</t>
         </is>
       </c>
       <c r="U34" s="2" t="inlineStr">
         <is>
-          <t>23,15%</t>
+          <t>25,06%</t>
         </is>
       </c>
       <c r="V34" s="2" t="inlineStr">
         <is>
-          <t>20,18%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="W34" s="2" t="inlineStr">
         <is>
-          <t>25,56%</t>
+          <t>26,03%</t>
         </is>
       </c>
     </row>
@@ -4252,32 +4252,32 @@
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>412746</t>
+          <t>461950</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>315066</t>
+          <t>419398</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>461063</t>
+          <t>504492</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>13,43%</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>9,34%</t>
+          <t>12,19%</t>
         </is>
       </c>
       <c r="I35" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="J35" s="2" t="inlineStr">
@@ -4287,32 +4287,32 @@
       </c>
       <c r="K35" s="2" t="inlineStr">
         <is>
-          <t>446026</t>
+          <t>516852</t>
         </is>
       </c>
       <c r="L35" s="2" t="inlineStr">
         <is>
-          <t>363086</t>
+          <t>481098</t>
         </is>
       </c>
       <c r="M35" s="2" t="inlineStr">
         <is>
-          <t>490105</t>
+          <t>553861</t>
         </is>
       </c>
       <c r="N35" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>14,23%</t>
         </is>
       </c>
       <c r="O35" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>13,25%</t>
         </is>
       </c>
       <c r="P35" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="Q35" s="2" t="inlineStr">
@@ -4322,32 +4322,32 @@
       </c>
       <c r="R35" s="2" t="inlineStr">
         <is>
-          <t>858771</t>
+          <t>978802</t>
         </is>
       </c>
       <c r="S35" s="2" t="inlineStr">
         <is>
-          <t>740352</t>
+          <t>921991</t>
         </is>
       </c>
       <c r="T35" s="2" t="inlineStr">
         <is>
-          <t>942577</t>
+          <t>1041285</t>
         </is>
       </c>
       <c r="U35" s="2" t="inlineStr">
         <is>
-          <t>12,36%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="V35" s="2" t="inlineStr">
         <is>
-          <t>10,65%</t>
+          <t>13,04%</t>
         </is>
       </c>
       <c r="W35" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>14,72%</t>
         </is>
       </c>
     </row>
@@ -4365,32 +4365,32 @@
       </c>
       <c r="D36" s="2" t="inlineStr">
         <is>
-          <t>539556</t>
+          <t>583851</t>
         </is>
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>410946</t>
+          <t>538371</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>602480</t>
+          <t>634190</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>15,99%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>12,18%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="I36" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>18,44%</t>
         </is>
       </c>
       <c r="J36" s="2" t="inlineStr">
@@ -4400,32 +4400,32 @@
       </c>
       <c r="K36" s="2" t="inlineStr">
         <is>
-          <t>534719</t>
+          <t>602893</t>
         </is>
       </c>
       <c r="L36" s="2" t="inlineStr">
         <is>
-          <t>443747</t>
+          <t>561459</t>
         </is>
       </c>
       <c r="M36" s="2" t="inlineStr">
         <is>
-          <t>589428</t>
+          <t>646120</t>
         </is>
       </c>
       <c r="N36" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>16,6%</t>
         </is>
       </c>
       <c r="O36" s="2" t="inlineStr">
         <is>
-          <t>12,41%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="P36" s="2" t="inlineStr">
         <is>
-          <t>16,48%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="Q36" s="2" t="inlineStr">
@@ -4435,32 +4435,32 @@
       </c>
       <c r="R36" s="2" t="inlineStr">
         <is>
-          <t>1074275</t>
+          <t>1186744</t>
         </is>
       </c>
       <c r="S36" s="2" t="inlineStr">
         <is>
-          <t>933644</t>
+          <t>1117814</t>
         </is>
       </c>
       <c r="T36" s="2" t="inlineStr">
         <is>
-          <t>1165584</t>
+          <t>1249483</t>
         </is>
       </c>
       <c r="U36" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="V36" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="W36" s="2" t="inlineStr">
         <is>
-          <t>16,77%</t>
+          <t>17,67%</t>
         </is>
       </c>
     </row>
@@ -4478,32 +4478,32 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>1659477</t>
+          <t>1513178</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>1513176</t>
+          <t>1447174</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>2135626</t>
+          <t>1578404</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>49,17%</t>
+          <t>43,99%</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>44,84%</t>
+          <t>42,07%</t>
         </is>
       </c>
       <c r="I37" s="2" t="inlineStr">
         <is>
-          <t>63,28%</t>
+          <t>45,89%</t>
         </is>
       </c>
       <c r="J37" s="2" t="inlineStr">
@@ -4513,32 +4513,32 @@
       </c>
       <c r="K37" s="2" t="inlineStr">
         <is>
-          <t>1748885</t>
+          <t>1620989</t>
         </is>
       </c>
       <c r="L37" s="2" t="inlineStr">
         <is>
-          <t>1600683</t>
+          <t>1562683</t>
         </is>
       </c>
       <c r="M37" s="2" t="inlineStr">
         <is>
-          <t>2096566</t>
+          <t>1670917</t>
         </is>
       </c>
       <c r="N37" s="2" t="inlineStr">
         <is>
-          <t>48,91%</t>
+          <t>44,63%</t>
         </is>
       </c>
       <c r="O37" s="2" t="inlineStr">
         <is>
-          <t>44,77%</t>
+          <t>43,02%</t>
         </is>
       </c>
       <c r="P37" s="2" t="inlineStr">
         <is>
-          <t>58,64%</t>
+          <t>46,0%</t>
         </is>
       </c>
       <c r="Q37" s="2" t="inlineStr">
@@ -4548,32 +4548,32 @@
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>3408362</t>
+          <t>3134167</t>
         </is>
       </c>
       <c r="S37" s="2" t="inlineStr">
         <is>
-          <t>3165090</t>
+          <t>3047234</t>
         </is>
       </c>
       <c r="T37" s="2" t="inlineStr">
         <is>
-          <t>3894822</t>
+          <t>3214823</t>
         </is>
       </c>
       <c r="U37" s="2" t="inlineStr">
         <is>
-          <t>49,04%</t>
+          <t>44,32%</t>
         </is>
       </c>
       <c r="V37" s="2" t="inlineStr">
         <is>
-          <t>45,54%</t>
+          <t>43,09%</t>
         </is>
       </c>
       <c r="W37" s="2" t="inlineStr">
         <is>
-          <t>56,04%</t>
+          <t>45,46%</t>
         </is>
       </c>
     </row>
@@ -4591,17 +4591,17 @@
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>3374879</t>
+          <t>3439854</t>
         </is>
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>3374879</t>
+          <t>3439854</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
         <is>
-          <t>3374879</t>
+          <t>3439854</t>
         </is>
       </c>
       <c r="G38" s="2" t="inlineStr">
@@ -4626,17 +4626,17 @@
       </c>
       <c r="K38" s="2" t="inlineStr">
         <is>
-          <t>3575591</t>
+          <t>3632263</t>
         </is>
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>3575591</t>
+          <t>3632263</t>
         </is>
       </c>
       <c r="M38" s="2" t="inlineStr">
         <is>
-          <t>3575591</t>
+          <t>3632263</t>
         </is>
       </c>
       <c r="N38" s="2" t="inlineStr">
@@ -4661,17 +4661,17 @@
       </c>
       <c r="R38" s="2" t="inlineStr">
         <is>
-          <t>6950470</t>
+          <t>7072117</t>
         </is>
       </c>
       <c r="S38" s="2" t="inlineStr">
         <is>
-          <t>6950470</t>
+          <t>7072117</t>
         </is>
       </c>
       <c r="T38" s="2" t="inlineStr">
         <is>
-          <t>6950470</t>
+          <t>7072117</t>
         </is>
       </c>
       <c r="U38" s="2" t="inlineStr">
